--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2012-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2012-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80C56DB6-2F74-481D-8DFC-53F1CBF60B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{249B3C11-8F0C-405D-A76A-CE1F221D4783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{A93E1613-94B3-42E8-BE1C-DA0D51A93F66}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{67DEC2F3-3F5C-4A28-8E59-F5183C5EBF03}"/>
   </bookViews>
   <sheets>
     <sheet name="2012-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1604,30 +1604,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BC11DB9-5AFF-43F3-8BE6-FFAB5A1C4C43}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB307313-3F2A-4F53-9C88-E3EC2F4B873D}">
   <dimension ref="A1:X62"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1661,7 +1661,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1697,7 +1697,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1817,7 +1817,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1889,7 +1889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="41">
         <v>2024</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2023</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="41">
         <v>2022</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>6.96</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2623,7 +2623,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>29</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>2.38</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="39">
         <v>2021</v>
       </c>
@@ -2769,7 +2769,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="43" t="s">
         <v>29</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>7.14</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="44"/>
       <c r="B19" s="44"/>
       <c r="C19" s="20" t="s">
@@ -2871,7 +2871,7 @@
       <c r="W19" s="50"/>
       <c r="X19" s="46"/>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2945,7 +2945,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="41">
         <v>2020</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>3.47</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>29</v>
       </c>
@@ -3091,7 +3091,7 @@
         <v>3.47</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>29</v>
       </c>
@@ -3165,7 +3165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>29</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="39">
         <v>2019</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>7.69</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>29</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>7.69</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="41">
         <v>2018</v>
       </c>
@@ -3457,7 +3457,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="39">
         <v>2017</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>5.23</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="41">
         <v>2016</v>
       </c>
@@ -3601,7 +3601,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="39">
         <v>2015</v>
       </c>
@@ -3673,7 +3673,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="41">
         <v>2014</v>
       </c>
@@ -3745,7 +3745,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="39">
         <v>2013</v>
       </c>
@@ -3817,7 +3817,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="41">
         <v>2012</v>
       </c>
@@ -3889,7 +3889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="39">
         <v>2011</v>
       </c>
@@ -3961,7 +3961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="41">
         <v>2010</v>
       </c>
@@ -4033,7 +4033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="39">
         <v>2009</v>
       </c>
@@ -4105,7 +4105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="41">
         <v>2008</v>
       </c>
@@ -4177,7 +4177,7 @@
         <v>8.82</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="39">
         <v>2007</v>
       </c>
@@ -4249,7 +4249,7 @@
         <v>8.33</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="41">
         <v>2006</v>
       </c>
@@ -4321,7 +4321,7 @@
         <v>6.63</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="39">
         <v>2005</v>
       </c>
@@ -4393,7 +4393,7 @@
         <v>7.45</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="41">
         <v>2004</v>
       </c>
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="39">
         <v>2003</v>
       </c>
@@ -4537,7 +4537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="41">
         <v>2002</v>
       </c>
@@ -4609,7 +4609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="39">
         <v>2001</v>
       </c>
@@ -4681,7 +4681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="41">
         <v>2000</v>
       </c>
@@ -4753,7 +4753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="39">
         <v>1999</v>
       </c>
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="41">
         <v>1998</v>
       </c>
@@ -4897,7 +4897,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="39">
         <v>1997</v>
       </c>
@@ -4969,7 +4969,7 @@
         <v>8.66</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="41">
         <v>1996</v>
       </c>
@@ -5041,7 +5041,7 @@
         <v>9.15</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="39">
         <v>1995</v>
       </c>
@@ -5113,7 +5113,7 @@
         <v>6.94</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="41">
         <v>1994</v>
       </c>
@@ -5185,7 +5185,7 @@
         <v>6.49</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="39">
         <v>1993</v>
       </c>
@@ -5257,7 +5257,7 @@
         <v>6.23</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="41">
         <v>1992</v>
       </c>
@@ -5329,7 +5329,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="39">
         <v>1991</v>
       </c>
@@ -5401,7 +5401,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="51">
         <v>1990</v>
       </c>
@@ -5473,7 +5473,7 @@
         <v>3.36</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="53"/>
       <c r="B56" s="54"/>
       <c r="C56" s="22" t="s">
@@ -5501,7 +5501,7 @@
       <c r="W56" s="60"/>
       <c r="X56" s="56"/>
     </row>
-    <row r="57" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="39">
         <v>1989</v>
       </c>
@@ -5573,7 +5573,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="41">
         <v>1988</v>
       </c>
@@ -5645,7 +5645,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="39">
         <v>1987</v>
       </c>
@@ -5717,7 +5717,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="41">
         <v>1985</v>
       </c>
@@ -5789,7 +5789,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A61" s="39">
         <v>1984</v>
       </c>
@@ -5861,7 +5861,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A62" s="41" t="s">
         <v>67</v>
       </c>
